--- a/TMC_Vision_Accuracy_Dashboard.xlsx
+++ b/TMC_Vision_Accuracy_Dashboard.xlsx
@@ -7044,7 +7044,7 @@
         <v/>
       </c>
       <c r="K2" s="6">
-        <f>SQRT(2*((G2/E2)-(F2/E2))^2/((F2/E2)+(G2/E2)))</f>
+        <f>IF(E2="","",SQRT(2*((G2/E2)-(F2/E2))^2/((F2/E2)+(G2/E2))))</f>
         <v/>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="K3" s="6">
-        <f>SQRT(2*((G3/E3)-(F3/E3))^2/((F3/E3)+(G3/E3)))</f>
+        <f>IF(E3="","",SQRT(2*((G3/E3)-(F3/E3))^2/((F3/E3)+(G3/E3))))</f>
         <v/>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
         <v/>
       </c>
       <c r="K4" s="6">
-        <f>SQRT(2*((G4/E4)-(F4/E4))^2/((F4/E4)+(G4/E4)))</f>
+        <f>IF(E4="","",SQRT(2*((G4/E4)-(F4/E4))^2/((F4/E4)+(G4/E4))))</f>
         <v/>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>SQRT(2*((G5/E5)-(F5/E5))^2/((F5/E5)+(G5/E5)))</f>
+        <f>IF(E5="","",SQRT(2*((G5/E5)-(F5/E5))^2/((F5/E5)+(G5/E5))))</f>
         <v/>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>SQRT(2*((G6/E6)-(F6/E6))^2/((F6/E6)+(G6/E6)))</f>
+        <f>IF(E6="","",SQRT(2*((G6/E6)-(F6/E6))^2/((F6/E6)+(G6/E6))))</f>
         <v/>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>SQRT(2*((G7/E7)-(F7/E7))^2/((F7/E7)+(G7/E7)))</f>
+        <f>IF(E7="","",SQRT(2*((G7/E7)-(F7/E7))^2/((F7/E7)+(G7/E7))))</f>
         <v/>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>SQRT(2*((G8/E8)-(F8/E8))^2/((F8/E8)+(G8/E8)))</f>
+        <f>IF(E8="","",SQRT(2*((G8/E8)-(F8/E8))^2/((F8/E8)+(G8/E8))))</f>
         <v/>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>SQRT(2*((G9/E9)-(F9/E9))^2/((F9/E9)+(G9/E9)))</f>
+        <f>IF(E9="","",SQRT(2*((G9/E9)-(F9/E9))^2/((F9/E9)+(G9/E9))))</f>
         <v/>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>SQRT(2*((G10/E10)-(F10/E10))^2/((F10/E10)+(G10/E10)))</f>
+        <f>IF(E10="","",SQRT(2*((G10/E10)-(F10/E10))^2/((F10/E10)+(G10/E10))))</f>
         <v/>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>SQRT(2*((G11/E11)-(F11/E11))^2/((F11/E11)+(G11/E11)))</f>
+        <f>IF(E11="","",SQRT(2*((G11/E11)-(F11/E11))^2/((F11/E11)+(G11/E11))))</f>
         <v/>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>SQRT(2*((G12/E12)-(F12/E12))^2/((F12/E12)+(G12/E12)))</f>
+        <f>IF(E12="","",SQRT(2*((G12/E12)-(F12/E12))^2/((F12/E12)+(G12/E12))))</f>
         <v/>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>SQRT(2*((G13/E13)-(F13/E13))^2/((F13/E13)+(G13/E13)))</f>
+        <f>IF(E13="","",SQRT(2*((G13/E13)-(F13/E13))^2/((F13/E13)+(G13/E13))))</f>
         <v/>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>SQRT(2*((G14/E14)-(F14/E14))^2/((F14/E14)+(G14/E14)))</f>
+        <f>IF(E14="","",SQRT(2*((G14/E14)-(F14/E14))^2/((F14/E14)+(G14/E14))))</f>
         <v/>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>SQRT(2*((G15/E15)-(F15/E15))^2/((F15/E15)+(G15/E15)))</f>
+        <f>IF(E15="","",SQRT(2*((G15/E15)-(F15/E15))^2/((F15/E15)+(G15/E15))))</f>
         <v/>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>SQRT(2*((G16/E16)-(F16/E16))^2/((F16/E16)+(G16/E16)))</f>
+        <f>IF(E16="","",SQRT(2*((G16/E16)-(F16/E16))^2/((F16/E16)+(G16/E16))))</f>
         <v/>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>SQRT(2*((G17/E17)-(F17/E17))^2/((F17/E17)+(G17/E17)))</f>
+        <f>IF(E17="","",SQRT(2*((G17/E17)-(F17/E17))^2/((F17/E17)+(G17/E17))))</f>
         <v/>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>SQRT(2*((G18/E18)-(F18/E18))^2/((F18/E18)+(G18/E18)))</f>
+        <f>IF(E18="","",SQRT(2*((G18/E18)-(F18/E18))^2/((F18/E18)+(G18/E18))))</f>
         <v/>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>SQRT(2*((G19/E19)-(F19/E19))^2/((F19/E19)+(G19/E19)))</f>
+        <f>IF(E19="","",SQRT(2*((G19/E19)-(F19/E19))^2/((F19/E19)+(G19/E19))))</f>
         <v/>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>SQRT(2*((G20/E20)-(F20/E20))^2/((F20/E20)+(G20/E20)))</f>
+        <f>IF(E20="","",SQRT(2*((G20/E20)-(F20/E20))^2/((F20/E20)+(G20/E20))))</f>
         <v/>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>SQRT(2*((G21/E21)-(F21/E21))^2/((F21/E21)+(G21/E21)))</f>
+        <f>IF(E21="","",SQRT(2*((G21/E21)-(F21/E21))^2/((F21/E21)+(G21/E21))))</f>
         <v/>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>SQRT(2*((G22/E22)-(F22/E22))^2/((F22/E22)+(G22/E22)))</f>
+        <f>IF(E22="","",SQRT(2*((G22/E22)-(F22/E22))^2/((F22/E22)+(G22/E22))))</f>
         <v/>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>SQRT(2*((G23/E23)-(F23/E23))^2/((F23/E23)+(G23/E23)))</f>
+        <f>IF(E23="","",SQRT(2*((G23/E23)-(F23/E23))^2/((F23/E23)+(G23/E23))))</f>
         <v/>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>SQRT(2*((G24/E24)-(F24/E24))^2/((F24/E24)+(G24/E24)))</f>
+        <f>IF(E24="","",SQRT(2*((G24/E24)-(F24/E24))^2/((F24/E24)+(G24/E24))))</f>
         <v/>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>SQRT(2*((G25/E25)-(F25/E25))^2/((F25/E25)+(G25/E25)))</f>
+        <f>IF(E25="","",SQRT(2*((G25/E25)-(F25/E25))^2/((F25/E25)+(G25/E25))))</f>
         <v/>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>SQRT(2*((G26/E26)-(F26/E26))^2/((F26/E26)+(G26/E26)))</f>
+        <f>IF(E26="","",SQRT(2*((G26/E26)-(F26/E26))^2/((F26/E26)+(G26/E26))))</f>
         <v/>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>SQRT(2*((G27/E27)-(F27/E27))^2/((F27/E27)+(G27/E27)))</f>
+        <f>IF(E27="","",SQRT(2*((G27/E27)-(F27/E27))^2/((F27/E27)+(G27/E27))))</f>
         <v/>
       </c>
     </row>
@@ -8214,7 +8214,7 @@
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>SQRT(2*((G28/E28)-(F28/E28))^2/((F28/E28)+(G28/E28)))</f>
+        <f>IF(E28="","",SQRT(2*((G28/E28)-(F28/E28))^2/((F28/E28)+(G28/E28))))</f>
         <v/>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>SQRT(2*((G29/E29)-(F29/E29))^2/((F29/E29)+(G29/E29)))</f>
+        <f>IF(E29="","",SQRT(2*((G29/E29)-(F29/E29))^2/((F29/E29)+(G29/E29))))</f>
         <v/>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>SQRT(2*((G30/E30)-(F30/E30))^2/((F30/E30)+(G30/E30)))</f>
+        <f>IF(E30="","",SQRT(2*((G30/E30)-(F30/E30))^2/((F30/E30)+(G30/E30))))</f>
         <v/>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>SQRT(2*((G31/E31)-(F31/E31))^2/((F31/E31)+(G31/E31)))</f>
+        <f>IF(E31="","",SQRT(2*((G31/E31)-(F31/E31))^2/((F31/E31)+(G31/E31))))</f>
         <v/>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>SQRT(2*((G32/E32)-(F32/E32))^2/((F32/E32)+(G32/E32)))</f>
+        <f>IF(E32="","",SQRT(2*((G32/E32)-(F32/E32))^2/((F32/E32)+(G32/E32))))</f>
         <v/>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>SQRT(2*((G33/E33)-(F33/E33))^2/((F33/E33)+(G33/E33)))</f>
+        <f>IF(E33="","",SQRT(2*((G33/E33)-(F33/E33))^2/((F33/E33)+(G33/E33))))</f>
         <v/>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>SQRT(2*((G34/E34)-(F34/E34))^2/((F34/E34)+(G34/E34)))</f>
+        <f>IF(E34="","",SQRT(2*((G34/E34)-(F34/E34))^2/((F34/E34)+(G34/E34))))</f>
         <v/>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>SQRT(2*((G35/E35)-(F35/E35))^2/((F35/E35)+(G35/E35)))</f>
+        <f>IF(E35="","",SQRT(2*((G35/E35)-(F35/E35))^2/((F35/E35)+(G35/E35))))</f>
         <v/>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>SQRT(2*((G36/E36)-(F36/E36))^2/((F36/E36)+(G36/E36)))</f>
+        <f>IF(E36="","",SQRT(2*((G36/E36)-(F36/E36))^2/((F36/E36)+(G36/E36))))</f>
         <v/>
       </c>
     </row>

--- a/TMC_Vision_Accuracy_Dashboard.xlsx
+++ b/TMC_Vision_Accuracy_Dashboard.xlsx
@@ -394,8 +394,15 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
+            <size val="7"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E78"/>
+              </a:solidFill>
               <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1F4E78"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -510,8 +517,15 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
+            <size val="7"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E78"/>
+              </a:solidFill>
               <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1F4E78"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1025,8 +1039,15 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
+            <size val="7"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E78"/>
+              </a:solidFill>
               <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1F4E78"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
